--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4053-830-CM25</t>
+          <t>1432083-887-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14443.03</v>
+        <v>3075.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1305560-170-CM25</t>
+          <t>4053-830-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5065.24</v>
+        <v>14443.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5751-5704-CM25</t>
+          <t>1305560-170-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14644.5</v>
+        <v>5065.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1432083-2338-CM25</t>
+          <t>5751-5704-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>75399.23</v>
+        <v>14644.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1191382-1-CM26</t>
+          <t>1432083-2338-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>16790.64</v>
+        <v>75399.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2910-4-CM26</t>
+          <t>1191382-1-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8957</v>
+        <v>16790.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2909-32-CM26</t>
+          <t>2910-4-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5829.81</v>
+        <v>8957</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1035685-26-CM26</t>
+          <t>2909-32-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>64193.03</v>
+        <v>5829.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057545-161-CM26</t>
+          <t>1035685-26-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3065.34</v>
+        <v>64193.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1422032-10-CM26</t>
+          <t>1057545-161-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1218.46</v>
+        <v>3065.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1191382-7-CM26</t>
+          <t>1422032-10-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>37120.15</v>
+        <v>1218.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2909-106-CM26</t>
+          <t>1191382-7-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>709.26</v>
+        <v>37120.15</v>
       </c>
     </row>
     <row r="14">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5955-163-CM26</t>
+          <t>2909-106-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4746.03</v>
+        <v>709.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3335-260-CM26</t>
+          <t>5955-163-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>42250.95</v>
+        <v>4746.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3850-136-CM26</t>
+          <t>3335-260-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3854.95</v>
+        <v>42250.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3335-294-CM26</t>
+          <t>3850-136-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3354.91</v>
+        <v>3854.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>926853-11-CM26</t>
+          <t>3335-294-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4952.39</v>
+        <v>3354.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3335-372-CM26</t>
+          <t>926853-11-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4422.52</v>
+        <v>4952.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2910-71-CM26</t>
+          <t>3335-372-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5537.03</v>
+        <v>4422.52</v>
       </c>
     </row>
     <row r="22">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1107282-64-CM26</t>
+          <t>2910-71-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>923.4400000000001</v>
+        <v>5537.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1422032-25-CM26</t>
+          <t>1107282-64-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>21628.01</v>
+        <v>923.4400000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3335-444-CM26</t>
+          <t>1422032-25-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5224.1</v>
+        <v>21628.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3623-242-CM26</t>
+          <t>3335-444-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6045.1</v>
+        <v>5224.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3335-506-CM26</t>
+          <t>3623-242-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.500-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>22457.37</v>
+        <v>6045.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1432083-1093-CM26</t>
+          <t>3335-506-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6047.97</v>
+        <v>22457.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1432083-1094-CM26</t>
+          <t>1432083-1093-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>916.29</v>
+        <v>6047.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1432083-1102-CM26</t>
+          <t>1432083-1094-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1044.8</v>
+        <v>916.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1432083-1005-CM26</t>
+          <t>1432083-1102-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15499.75</v>
+        <v>1044.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1432083-1201-CM26</t>
+          <t>1432083-1005-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3560.43</v>
+        <v>15499.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1432083-1266-CM26</t>
+          <t>1432083-1201-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>849.36</v>
+        <v>3560.43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3623-291-CM26</t>
+          <t>1432083-1266-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4923.7</v>
+        <v>849.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1457902-15-CM26</t>
+          <t>3623-291-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.200.500-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>440.3</v>
+        <v>4923.7</v>
       </c>
     </row>
     <row r="36">
@@ -2649,7 +2649,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1422032-65-CM26</t>
+          <t>1457902-15-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t xml:space="preserve">Oficina de Seguimiento </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>528.36</v>
+        <v>440.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1432083-1658-CM26</t>
+          <t>1422032-65-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1134</v>
+        <v>528.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1457902-16-CM26</t>
+          <t>1432083-1658-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,22 +2786,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>9830.59</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1723-425-CM26</t>
+          <t>1457902-16-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,22 +2847,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t xml:space="preserve">Oficina de Seguimiento </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>213.01</v>
+        <v>9830.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1723-426-CM26</t>
+          <t>1723-425-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1134</v>
+        <v>213.01</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1432083-1683-CM26</t>
+          <t>1723-426-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2130.1</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>696750-28-CM26</t>
+          <t>1432083-1683-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7758.7</v>
+        <v>2130.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1432083-1724-CM26</t>
+          <t>696750-28-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2373.01</v>
+        <v>7758.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1432083-1711-CM26</t>
+          <t>1432083-1724-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4160.24</v>
+        <v>2373.01</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1432083-1713-CM26</t>
+          <t>1432083-1780-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>15624.03</v>
+        <v>1910.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1432083-1780-CM26</t>
+          <t>1432083-1711-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1910.99</v>
+        <v>4160.24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1723-444-CM26</t>
+          <t>1432083-1713-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,6 +3375,67 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
+        <v>15624.03</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1723-444-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>541.9299999999999</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1432083-887-CM25</t>
+          <t>1305560-12-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,17 +524,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3075.56</v>
+        <v>31927.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4053-830-CM25</t>
+          <t>5955-44-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14443.03</v>
+        <v>9746.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1305560-170-CM25</t>
+          <t>5418-21-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5065.24</v>
+        <v>10512.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5751-5704-CM25</t>
+          <t>3850-85-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14644.5</v>
+        <v>3923.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1432083-2338-CM25</t>
+          <t>3850-119-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>75399.23</v>
+        <v>9705.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1191382-1-CM26</t>
+          <t>2910-79-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>16790.64</v>
+        <v>7453.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2910-4-CM26</t>
+          <t>1305560-96-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8957</v>
+        <v>4728.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2909-32-CM26</t>
+          <t>926853-29-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5829.81</v>
+        <v>2779.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1035685-26-CM26</t>
+          <t>3335-515-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,28 +1057,28 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>64193.03</v>
+        <v>10798.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057545-161-CM26</t>
+          <t>1267885-2734-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3065.34</v>
+        <v>2852.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1422032-10-CM26</t>
+          <t>1267885-2733-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1218.46</v>
+        <v>24169.61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1191382-7-CM26</t>
+          <t>2909-328-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>37120.15</v>
+        <v>11297.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2909-105-CM26</t>
+          <t>1191382-15-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,43 +1301,43 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4900.47</v>
+        <v>16838.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2909-106-CM26</t>
+          <t>3335-785-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,43 +1362,43 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>709.26</v>
+        <v>13692.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5955-163-CM26</t>
+          <t>1432083-887-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,43 +1423,43 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4746.03</v>
+        <v>3075.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3335-260-CM26</t>
+          <t>1432083-900-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>42250.95</v>
+        <v>8232.360000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3850-136-CM26</t>
+          <t>1432083-905-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3854.95</v>
+        <v>10639.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3335-294-CM26</t>
+          <t>1079694-253-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,28 +1606,28 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3354.91</v>
+        <v>9059.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>926853-11-CM26</t>
+          <t>1432083-1124-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,43 +1667,43 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4952.39</v>
+        <v>4351.07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3335-372-CM26</t>
+          <t>1432083-1162-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,28 +1728,28 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4422.52</v>
+        <v>8037.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3789-212-CM26</t>
+          <t>1432083-1224-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3421.96</v>
+        <v>4053.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2910-71-CM26</t>
+          <t>1432083-1277-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,43 +1850,43 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5537.03</v>
+        <v>6198.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1107282-64-CM26</t>
+          <t>1432083-1327-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,43 +1911,43 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>923.4400000000001</v>
+        <v>3071.34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1422032-25-CM26</t>
+          <t>1432083-1395-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,43 +1972,43 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>21628.01</v>
+        <v>31439.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3335-444-CM26</t>
+          <t>1305560-170-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,28 +2033,28 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5224.1</v>
+        <v>5065.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3623-242-CM26</t>
+          <t>4053-830-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,43 +2094,43 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6045.1</v>
+        <v>14443.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3335-506-CM26</t>
+          <t>5751-5704-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>22457.37</v>
+        <v>14644.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1432083-1093-CM26</t>
+          <t>1432083-2338-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6047.97</v>
+        <v>75399.23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1432083-1094-CM26</t>
+          <t>1191382-1-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>916.29</v>
+        <v>16790.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1432083-1102-CM26</t>
+          <t>2910-4-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1044.8</v>
+        <v>8957</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1432083-1005-CM26</t>
+          <t>2909-32-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15499.75</v>
+        <v>5829.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1432083-1201-CM26</t>
+          <t>1035685-26-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3560.43</v>
+        <v>64193.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1432083-1266-CM26</t>
+          <t>1057545-161-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>849.36</v>
+        <v>3065.34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3623-291-CM26</t>
+          <t>1422032-10-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4923.7</v>
+        <v>1218.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4053-401-CM26</t>
+          <t>2909-106-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>18396.81</v>
+        <v>709.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1457902-15-CM26</t>
+          <t>2909-105-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>440.3</v>
+        <v>4900.47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1422032-65-CM26</t>
+          <t>1191382-7-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>528.36</v>
+        <v>37120.15</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1432083-1658-CM26</t>
+          <t>5955-163-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1134</v>
+        <v>4746.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1457902-16-CM26</t>
+          <t>3335-260-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9830.59</v>
+        <v>42250.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1723-425-CM26</t>
+          <t>3850-136-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>213.01</v>
+        <v>3854.95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1723-426-CM26</t>
+          <t>3335-294-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1134</v>
+        <v>3354.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1432083-1683-CM26</t>
+          <t>926853-11-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2130.1</v>
+        <v>4952.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>696750-28-CM26</t>
+          <t>3335-372-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7758.7</v>
+        <v>4422.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1432083-1724-CM26</t>
+          <t>2910-71-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2373.01</v>
+        <v>5537.03</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1432083-1780-CM26</t>
+          <t>3789-212-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1910.99</v>
+        <v>3421.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1432083-1711-CM26</t>
+          <t>1107282-64-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,27 +3269,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4160.24</v>
+        <v>923.4400000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1432083-1713-CM26</t>
+          <t>1422032-25-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>15624.03</v>
+        <v>21628.01</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1723-444-CM26</t>
+          <t>3335-444-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,7 +3436,1654 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
+        <v>5224.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3623-242-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.200.500-7</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>6045.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3335-506-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>22457.37</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1432083-1093-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>6047.97</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1432083-1094-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>916.29</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1432083-1102-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>1044.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1432083-1005-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>15499.75</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1432083-1201-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>3560.43</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1432083-1266-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>849.36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3623-291-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.200.500-7</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>4923.7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1457902-15-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oficina de Seguimiento </t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>440.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4053-401-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.200.400-0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>18396.81</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1422032-65-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>65.035.343-9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>528.36</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1432083-1658-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1457902-16-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oficina de Seguimiento </t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>9830.59</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1723-425-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>213.01</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1723-426-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>696750-28-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>7758.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1432083-1683-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>2130.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1432083-1724-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>2373.01</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1432083-1711-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>4160.24</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1432083-1713-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>15624.03</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1432083-1780-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>1910.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1723-444-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
         <v>541.9299999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1432083-1878-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>2547.98</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3335-944-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>2209.12</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3850-404-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>69.201.000-0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>2450.13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1432083-2140-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>9492.059999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2909-106-CM26</t>
+          <t>2909-105-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>709.26</v>
+        <v>4900.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2909-105-CM26</t>
+          <t>2909-106-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4900.47</v>
+        <v>709.26</v>
       </c>
     </row>
     <row r="38">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3259,7 +3259,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1107282-64-CM26</t>
+          <t>1422032-25-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>923.4400000000001</v>
+        <v>21628.01</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1422032-25-CM26</t>
+          <t>3335-444-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>21628.01</v>
+        <v>5224.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3335-444-CM26</t>
+          <t>3623-242-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.500-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5224.1</v>
+        <v>6045.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3623-242-CM26</t>
+          <t>3335-506-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6045.1</v>
+        <v>22457.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3335-506-CM26</t>
+          <t>1432083-1094-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>22457.37</v>
+        <v>916.29</v>
       </c>
     </row>
     <row r="52">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1432083-1094-CM26</t>
+          <t>1432083-1102-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>916.29</v>
+        <v>1044.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1432083-1102-CM26</t>
+          <t>1432083-1005-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1044.8</v>
+        <v>15499.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1432083-1005-CM26</t>
+          <t>1432083-1201-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>15499.75</v>
+        <v>3560.43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1432083-1201-CM26</t>
+          <t>1432083-1266-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3560.43</v>
+        <v>849.36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1432083-1266-CM26</t>
+          <t>3623-291-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,22 +3884,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.500-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>849.36</v>
+        <v>4923.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3623-291-CM26</t>
+          <t>4053-401-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4923.7</v>
+        <v>18396.81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1457902-15-CM26</t>
+          <t>1422032-65-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,22 +4006,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>440.3</v>
+        <v>528.36</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4053-401-CM26</t>
+          <t>1432083-1658-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>18396.81</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1422032-65-CM26</t>
+          <t>1723-426-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>528.36</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1432083-1658-CM26</t>
+          <t>1723-425-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1134</v>
+        <v>213.01</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1457902-16-CM26</t>
+          <t>1432083-1683-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>9830.59</v>
+        <v>2130.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1723-425-CM26</t>
+          <t>696750-28-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>213.01</v>
+        <v>7758.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1723-426-CM26</t>
+          <t>1432083-1724-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1134</v>
+        <v>2373.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>696750-28-CM26</t>
+          <t>1432083-1711-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>7758.7</v>
+        <v>4160.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1432083-1683-CM26</t>
+          <t>1432083-1713-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2130.1</v>
+        <v>15624.03</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1432083-1724-CM26</t>
+          <t>1432083-1780-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2373.01</v>
+        <v>1910.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1432083-1711-CM26</t>
+          <t>1723-444-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4621,17 +4621,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4160.24</v>
+        <v>541.9299999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1432083-1713-CM26</t>
+          <t>1432083-1878-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>15624.03</v>
+        <v>2547.98</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1432083-1780-CM26</t>
+          <t>3335-944-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1910.99</v>
+        <v>2209.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1723-444-CM26</t>
+          <t>3850-404-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>541.9299999999999</v>
+        <v>2450.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1432083-1878-CM26</t>
+          <t>1432083-2140-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2547.98</v>
+        <v>9492.059999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3335-944-CM26</t>
+          <t>2905-614-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,27 +4916,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2209.12</v>
+        <v>8918.809999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3850-404-CM26</t>
+          <t>1422032-102-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2450.13</v>
+        <v>569.25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1432083-2140-CM26</t>
+          <t>5472-47-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,27 +5038,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,7 +5083,251 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>9492.059999999999</v>
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>5456-80-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>65.852.930-7</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>3226.89</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1078634-14-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.402.010-5</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1432083-2320-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>2019.87</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1107282-223-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>901.89</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
@@ -562,7 +562,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1793,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1858,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1984,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2049,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2114,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2179,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2244,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2309,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2374,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2561,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2626,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2691,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2756,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2882,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2947,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3012,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3077,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3142,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3207,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3272,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3337,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3463,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3528,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3593,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3658,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3723,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3788,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3853,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3979,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4044,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4109,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4174,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4239,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4304,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4369,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4434,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4499,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4625,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4751,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4816,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4881,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4946,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5011,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5076,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5141,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5206,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5271,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5336,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5462,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5527,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2708,7 +2708,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2909-105-CM26</t>
+          <t>1191382-7-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4900.47</v>
+        <v>37120.15</v>
       </c>
     </row>
     <row r="37">
@@ -2834,7 +2834,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1191382-7-CM26</t>
+          <t>2909-105-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>37120.15</v>
+        <v>4900.47</v>
       </c>
     </row>
     <row r="39">
@@ -3545,7 +3545,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3623-242-CM26</t>
+          <t>3335-506-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3565,17 +3565,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6045.1</v>
+        <v>22457.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3335-506-CM26</t>
+          <t>3623-242-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.500-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3669,13 +3669,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>22457.37</v>
+        <v>6045.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1432083-1094-CM26</t>
+          <t>1432083-1093-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>916.29</v>
+        <v>6047.97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1432083-1093-CM26</t>
+          <t>1432083-1094-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6047.97</v>
+        <v>916.29</v>
       </c>
     </row>
     <row r="53">
@@ -4321,7 +4321,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1723-426-CM26</t>
+          <t>1723-425-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1134</v>
+        <v>213.01</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1723-425-CM26</t>
+          <t>1723-426-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4426,17 +4426,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>213.01</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="63">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5600,6 +5600,266 @@
       </c>
       <c r="M80" s="2" t="n">
         <v>901.89</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>5418-237-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>COBROTECH SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.819.088-7</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>17238.34</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1457776-45-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>20091.75</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1432083-2570-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>2019.87</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1432083-2568-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>4039.74</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-rios.xlsx
@@ -4081,7 +4081,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
